--- a/data/trans_dic/P64D$bicicleta_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,74</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,55</t>
+          <t>0,18; 1,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,07</t>
+          <t>0,2; 1,14</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,51</t>
+          <t>0,27; 2,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,68</t>
+          <t>0,2; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,71</t>
+          <t>0,37; 1,66</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,75</t>
+          <t>1,84; 6,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 45,73</t>
+          <t>1,29; 50,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 33,86</t>
+          <t>2,16; 30,26</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,9</t>
+          <t>0,77; 1,96</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 20,62</t>
+          <t>0,54; 20,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,62</t>
+          <t>0,92; 11,01</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en bicicleta (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 4348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5228</t>
+          <t>0; 4346</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1183; 12455</t>
+          <t>1447; 12950</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 3624</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2450; 12853</t>
+          <t>2470; 13809</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1112; 8941</t>
+          <t>976; 8792</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>653; 5401</t>
+          <t>654; 5923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2527; 11609</t>
+          <t>2483; 11249</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7532; 27081</t>
+          <t>8665; 29102</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6423; 219321</t>
+          <t>6208; 244099</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19628; 321935</t>
+          <t>20528; 287688</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14805; 37416</t>
+          <t>15077; 38597</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8516; 301237</t>
+          <t>7930; 299486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31321; 398185</t>
+          <t>31386; 377216</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$bicicleta_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$bicicleta_2023-Habitat-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,61</t>
+          <t>0,64; 2,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,14</t>
+          <t>0,41; 1,62</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,47</t>
+          <t>0,77; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,61; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,66</t>
+          <t>1,03; 4,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,18</t>
+          <t>1,87; 5,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 50,9</t>
+          <t>1,17; 3,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 30,26</t>
+          <t>1,94; 4,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,96</t>
+          <t>1,25; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 20,5</t>
+          <t>0,69; 1,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 11,01</t>
+          <t>1,19; 2,23</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>3026</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4348</t>
+          <t>0; 12631</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4346</t>
+          <t>0; 13749</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>9567</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1447; 12950</t>
+          <t>3992; 16616</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3624</t>
+          <t>0; 4173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2470; 13809</t>
+          <t>4360; 17396</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>15300</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>976; 8792</t>
+          <t>3234; 27171</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>654; 5923</t>
+          <t>2067; 11018</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2483; 11249</t>
+          <t>7761; 35837</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>17105</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90963</t>
+          <t>27351</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8665; 29102</t>
+          <t>9652; 29015</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6208; 244099</t>
+          <t>5235; 16190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20528; 287688</t>
+          <t>18682; 40326</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24970</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>79179</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104150</t>
+          <t>55245</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15077; 38597</t>
+          <t>24122; 56489</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7930; 299486</t>
+          <t>10425; 24974</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31386; 377216</t>
+          <t>40842; 76760</t>
         </is>
       </c>
     </row>
